--- a/data/รายชื่อ_นพอ_ปี69_2569.xlsx
+++ b/data/รายชื่อ_นพอ_ปี69_2569.xlsx
@@ -8132,7 +8132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8291,49 +8291,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>min_hours_per_year</t>
+          <t>min_hours_per_semester</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>เกณฑ์ชั่วโมงขั้นต่ำต่อปี</t>
+          <t>เกณฑ์ชั่วโมงขั้นต่ำต่อภาคเรียน (เทอม)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>max_hours_scale</t>
+          <t>min_hours_per_year</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>เพดานชั่วโมงสะสมสูงสุด</t>
+          <t>เกณฑ์ชั่วโมงขั้นต่ำต่อปีการศึกษา</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>max_hours_scale</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>เพดานชั่วโมงสะสมสูงสุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>academic_year</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2569</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>ปีการศึกษา</t>
         </is>
